--- a/www/download/IND.gdp.s.du.EXI382.xlsx
+++ b/www/download/IND.gdp.s.du.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>37624.6283836973</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>60606.6112523945</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>66601.3052730638</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>69148.7584540321</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>73833.1936288925</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>88253.1701324743</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>91339.302806033</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>88768.3102422624</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>82085.5302223597</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>81227.7761305026</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>89413.0303499825</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>97802.0066122459</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>104445.5915207</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>107928.195665432</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>111667.066949177</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>130743.36350925</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>140172.011822235</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>156177.529552788</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>155346.413333335</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>144488.611668759</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>153192.24695431</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>139151.504251506</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>152157.079444895</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>155525.998352766</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>158950.320184371</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>146391.018565807</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>145608.56965307</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>15045.2527953491</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27659.3166033848</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>30456.7431723926</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>31462.8900602236</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32948.1996779712</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>39614.0087022591</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>39757.7119373542</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>38169.1111754865</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34609.4032547455</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34010.4772440022</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36691.8373536054</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>39229.9126387772</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>40358.9931889688</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41000.0727752865</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41589.3617184725</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>46056.1725541048</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>47986.1303661452</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>54158.5755441038</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>52401.5770700159</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>53119.1704019847</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>59935.7170573554</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>55314.7009057134</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>61928.4487133102</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>62265.1364080081</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>68586.282349441</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>65559.1335563581</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>64716.8355073611</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11862.4665187145</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>21249.2862349758</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23682.7319675376</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>24471.7143760501</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26048.1007034894</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>33000.757350839</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>33786.5804731424</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32885.9515260668</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29648.4099404755</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28757.9137205226</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30890.9884868874</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>33172.2312627416</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35061.0336548206</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35745.6814345954</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36166.6128246108</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>40778.8832475328</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>42741.1081059648</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>47672.2356931671</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>47072.7569122625</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>48399.1214309005</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>51424.9594838512</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>48110.8414080619</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>51164.419031722</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>49864.781671571</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>53512.4074132721</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>52041.1437083298</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>51003.6618793426</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19349.5786721656</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>36451.7349318547</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>38314.3542995899</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>37211.9755547703</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>36236.075602707</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>43462.3437310514</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>38583.3046306414</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>40045.6092746636</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36318.2797738633</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36122.4793876889</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>39575.1268778429</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>42535.247407354</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>45829.8361908341</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>47670.8541326941</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49139.7578213933</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>51886.4418964086</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>50178.6597412565</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>52302.5417312481</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>50248.9552423921</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49733.0365568036</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>58711.2177145734</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>55228.0078103374</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>60155.1037504975</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>68873.5388746144</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>72780.6969838321</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>75154.0313331296</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>78291.5411915633</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>389581.62130688</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>768307.663128487</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>804042.892351851</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>848621.429409456</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>891488.950139885</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1092099.96198214</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1093251.43847145</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>1077977.80875492</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>993126.655959471</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>973109.276227593</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>1103709.09270171</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>1214904.1842844</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>1236624.38836786</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1264599.75878396</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>1257835.6699784</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1466249.47656724</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1499872.66119426</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1656411.8977099</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1649023.27759769</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1665117.7024768</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1797992.08971825</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1407093.32296418</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1519899.5533729</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1587836.29012255</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1520539.81156365</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1488157.31234893</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1488984.65421198</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>44750.3577180234</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>92044.3271351967</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>82082.8227900045</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>90341.7582685322</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>95636.27218748</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>140448.97667167</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>143413.600698631</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>138406.435441311</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>128749.421662347</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>126431.682981776</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>139627.278010606</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>124058.103248512</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>158072.835630678</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>160736.712624488</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>160853.152630842</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>154417.370033312</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>190304.837699021</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>213882.426160889</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>213281.833222183</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>208059.683993352</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>213970.153921293</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>189844.270148103</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>190978.871911273</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>192093.784185029</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>199681.918116031</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>192514.135014267</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>189199.590986082</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.894</t>
+          <t>9076904.34094569</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.571</t>
+          <t>8877776.24502017</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8.385</t>
+          <t>9781525.60421033</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>8.722</t>
+          <t>10069200.8242276</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.951</t>
+          <t>10319802.0668634</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>10.743</t>
+          <t>12378016.1836753</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.776</t>
+          <t>12403670.9253236</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.421</t>
+          <t>11974673.4412206</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9.604</t>
+          <t>11010107.9016166</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9.225</t>
+          <t>10543388.9234679</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.773</t>
+          <t>11201114.961044</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.924</t>
+          <t>12491671.2427564</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>11.353</t>
+          <t>13033317.481732</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>10.966</t>
+          <t>12477162.9472845</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10.346</t>
+          <t>11851392.1550353</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>11.462</t>
+          <t>13151910.6309133</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>12.754</t>
+          <t>14617829.4020813</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>14.606</t>
+          <t>16743701.6640588</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>14.258</t>
+          <t>16422837.4400541</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>15.365</t>
+          <t>17832804.2168469</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>18.252</t>
+          <t>21430417.034102</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>20.009</t>
+          <t>23594220.8491387</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>20.846</t>
+          <t>24772041.297782</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>25317883.3091822</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>23.947</t>
+          <t>28683802.2393646</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>25.081</t>
+          <t>30002409.2293248</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>25.836</t>
+          <t>30920545.9517358</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1493.79837134516</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1922.89175049341</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2097.27123349426</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2166.96975687412</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2285.04351098543</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2714.84332395862</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2792.63660915219</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2847.97886755061</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2633.45031910222</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2618.00703761222</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3040.81272251802</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3376.09682416247</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3488.85939393602</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3714.59621013171</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3881.99519319745</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4287.93610053706</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4510.35058923702</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4865.15381953354</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4505.32505810622</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4256.08869187179</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4291.85559562859</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4193.90907028152</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4977.07245742268</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5211.119754698</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5911.71409328252</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6031.63471826184</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5860.07346648598</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27170.5600447157</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>44766.3560560405</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49992.2574830695</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>50616.9077095101</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>52986.3980757474</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>61716.7913816182</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>61009.9267423383</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>54550.9557432198</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>51483.6527919544</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49410.102399751</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>53878.1128651103</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>58537.9099843886</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>60310.7250489565</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>61096.5657123465</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>62211.598445127</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>68742.1261994176</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>71749.4540145531</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>77078.907335484</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>77537.6830884295</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>75633.8623238449</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>83299.7893752898</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>81156.5109148843</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>87122.9159245912</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>89649.2174263913</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>102959.558905633</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>104882.44637927</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>104764.32954206</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>125593.190127835</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>244497.875701525</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>263791.733066464</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>267200.318619973</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>282547.666944562</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>338991.881907838</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>338145.896269848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>322283.786924605</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>291874.767869375</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>280095.536291628</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>300007.797029213</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>315721.551370071</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>331035.455945603</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>337284.118420518</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>341995.878235792</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>379590.228242917</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>403276.304005627</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>455042.620841563</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>445993.539878296</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>474737.686430137</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>544980.107731001</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>478975.879844598</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>513120.934007349</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>536921.795896962</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>560247.083807312</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>538125.775877725</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>541273.103236474</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11316.5046867342</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>22584.6311331718</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>24537.203781469</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22741.9089532555</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19851.8277476391</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>33540.8397950222</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32226.1060666235</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>31548.3511311022</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29323.7519333099</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27707.1180555696</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>30402.579085301</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>33407.250840142</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34615.5352915641</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35268.5866555913</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34267.6099373719</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36287.6262910923</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>38142.80408791</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>42819.0219643764</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41618.165537241</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41624.0535410058</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>50655.3758643541</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>43290.184822476</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>45897.2558287778</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>45527.346087975</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>46789.1007847658</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>41852.9814976651</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>45066.9134480384</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>62668.7713721669</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>109150.259604509</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>119065.979339672</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>128313.113230816</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>141599.335596736</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>182802.150837199</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>186206.721577246</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>188266.093372559</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>179176.589949946</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>177778.402371401</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>197929.288950598</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>228149.77606841</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>241980.035572126</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>247036.974152177</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>234207.58335972</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>239905.363790184</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>240566.98723405</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>256048.55906578</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>234748.24278025</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>232479.317147626</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>258111.09646497</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>246989.914708342</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>261925.054227737</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>259687.480908882</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>286609.124111795</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>269685.138902615</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>266647.93492814</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6961.86472799434</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6776.90632568447</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7058.26632567561</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7119.49542201611</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7419.66597503075</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8269.35011244891</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8484.37303595003</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8051.70875111187</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7012.43466813219</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6991.14140450321</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7678.24681140434</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8569.03280506405</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9459.40522770702</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9599.66626960265</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9439.23360700455</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9431.54679587108</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9342.54352809343</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11289.7058026199</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11172.0682304526</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11421.0779077095</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12806.4266025654</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11579.2811224714</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12711.7932432182</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12917.8379241187</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14606.232688867</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14899.5186998771</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>15059.6464892529</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9932.94269094974</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19505.2999392134</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21779.8692799181</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>24468.6553930793</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>25821.7817454538</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>31410.066170604</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>31670.5681747551</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>30448.9801582758</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>28075.2647979486</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26652.0782785013</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28550.2583410482</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>31091.9404206806</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32493.292924375</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32787.227844081</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29266.1327896926</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35873.474418865</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>37197.7204583633</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41326.6946764539</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>40047.2269168199</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>39990.1403619054</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>46314.0875870164</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>41728.4571553608</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>45130.6558055809</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>44555.7268015145</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>50309.3553911439</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>45563.9575316593</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>45129.5357618171</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>64718.165831873</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>151003.447970812</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>166182.195362499</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>170205.198134786</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>179233.047966616</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>215996.764293401</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>214802.200901048</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>208242.884209473</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>186511.492422967</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>181538.490260595</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>198333.250988376</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>212285.294591879</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>219058.228570167</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>225061.256621762</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>227515.000745894</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>257062.164776215</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>267332.543892645</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>296564.166142332</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>288090.904891051</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>285512.495817665</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>321322.770065991</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>289322.021265662</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>300027.575313117</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>291536.8173633</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>308969.788578373</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>294545.261022385</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>289430.417686913</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>129085.958026159</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>208493.700726841</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>238696.626114185</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>245049.35769055</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>261270.869144239</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>306932.521672585</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>308833.139077722</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>302435.501864366</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>277545.99815774</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>269128.839278828</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>290035.486879555</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>317161.230449966</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>332514.410858881</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>335359.45726286</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>325091.992232134</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>362087.514703487</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>376669.977506712</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>418228.416470916</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>411685.703364341</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>423420.137178346</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>521326.475573749</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>550665.768780939</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>513568.436669203</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>486200.95147889</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>543734.695600009</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>538827.676604103</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>534939.906420099</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13875.5304489022</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>38089.0057548648</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41618.8819657191</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41734.5242377587</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>45186.1501518947</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>54489.0677156841</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>54555.0980112347</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>52663.9758755847</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>47998.2109901437</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>48178.2388685103</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>50964.5877466905</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>53945.7236852804</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>55850.450082606</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>56100.8133638857</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>54507.637860339</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>60639.3241895485</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>61669.9648238679</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>61437.7665742136</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>55309.7960354959</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>52148.1717914842</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>52372.6445667747</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>48078.5227059987</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>48362.810998476</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>52478.5919809569</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>56873.005963829</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>55750.304324964</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>56057.4971923022</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20851.8868364678</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>39966.250517876</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>42792.0902779671</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>43732.5796874667</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>46900.9420654915</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>57317.7824972456</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>56491.0480482764</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>56174.9732677822</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49627.0814994879</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49445.7840590028</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>52633.0268443952</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>52787.6069292395</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>56936.7656526323</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>56487.5971116969</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>52558.4871800852</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>59935.9597726381</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>62190.5700987758</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>69056.1388297827</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>66974.7185700693</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>69187.7367035911</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>77908.7099633129</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>75302.5192763346</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>78758.2150239344</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>82698.8335499091</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>95616.2825488183</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>94280.0363384966</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>95032.6605846756</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>6737554.09364913</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.712</t>
+          <t>5525601.31718384</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>6089409.78684063</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5.409</t>
+          <t>6243793.23060849</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.689</t>
+          <t>6558958.53465649</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6.957</t>
+          <t>8015620.99042488</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7.459</t>
+          <t>8585332.05569097</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8193187.5280138</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6.352</t>
+          <t>7281669.21520108</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6.461</t>
+          <t>7384555.41781377</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>6.865</t>
+          <t>7868524.31571451</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>7.302</t>
+          <t>8350011.43695771</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>7.474</t>
+          <t>8579755.11927454</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>7.582</t>
+          <t>8627492.50706898</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>7.535</t>
+          <t>8631571.2818542</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>8.672</t>
+          <t>9950027.29498779</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>8.923</t>
+          <t>10226987.5200434</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>9.888</t>
+          <t>11334897.52207</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>9.641</t>
+          <t>11105061.9769624</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>9.899</t>
+          <t>11488922.6292236</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>11.574</t>
+          <t>13589675.7829033</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>12.846</t>
+          <t>15147248.5160048</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>14.431</t>
+          <t>17149018.6415169</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15.684</t>
+          <t>18651537.7492462</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>16.409</t>
+          <t>19655211.0238383</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17.348</t>
+          <t>20752660.5659683</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>18.198</t>
+          <t>21779631.1042623</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>850036.293592379</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>807568.827385464</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>933874.963095589</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>961116.542237862</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>1021614.82932858</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1236125.97353736</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1241857.42408611</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1235823.64030302</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.967</t>
+          <t>1108723.36336616</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>1116821.27975516</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1273408.21384642</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1377511.60334706</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1417796.31212618</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>1460820.54975555</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1556892.72138201</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1738315.10885542</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>1860480.39624225</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1910718.7841049</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1.771</t>
+          <t>2039797.44503791</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>2091084.04593653</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>1.881</t>
+          <t>2208198.09722412</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2482651.29859679</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2.355</t>
+          <t>2798922.99075738</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2.421</t>
+          <t>2878530.72557742</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2958997.90698694</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>3156264.23907101</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2.728</t>
+          <t>3265143.8035184</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16051.6987961889</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11799.2543524531</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13381.3488799703</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14615.3184967678</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15858.2054720177</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>20072.1514343947</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20742.9412642792</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20525.2675909375</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>18403.0573305831</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>18660.0045301599</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20496.2662860069</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23136.1335279651</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>25011.3247971392</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>25638.7471389746</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24729.936456772</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24917.5542916252</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>24252.1050099342</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26167.8481149758</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>25396.5798136919</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>28023.1966713648</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>33715.0028311715</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>43984.907563208</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>53006.9258843928</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>52439.29083669</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>58004.12774496</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>62554.3279847588</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>64249.4647145709</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>74575.0697740805</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>186876.363125371</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>197937.34864394</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>207053.684507896</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>220451.981438914</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>261492.402670317</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>263446.191091022</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>266556.003061537</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>219606.591599927</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>237226.763577035</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>253811.298418853</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>269315.953519416</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>280248.020658488</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>282832.30751102</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>274242.400799515</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>306212.703940804</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>315442.465204416</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>346526.850723125</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>328429.652093342</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>328744.802729989</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>361969.42117211</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>329338.42814978</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>346463.463418319</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>341890.56398929</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>370478.520933191</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>341000.865446222</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>334336.83900087</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>202878.638706861</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>663590.337019303</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>722553.638404592</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>748932.414487031</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>775338.418927447</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>914923.14041521</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>913598.775546179</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>872930.452102856</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>787829.403722177</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>720406.932357746</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>765329.597534409</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>818071.234318035</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>850676.26025606</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>857459.635373884</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>790727.31205098</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>937398.770891669</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>967591.941376177</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>1073633.03197186</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>1050795.08866609</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>836101.641751135</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>977637.888113015</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>900437.035006606</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>997604.42626385</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>930728.780500083</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>947644.407013506</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>949933.188695393</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>919251.310214494</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>174097.660814194</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>209080.245905868</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>227045.941812167</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>232051.332921064</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>224609.583322174</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>266908.428966457</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>285211.980370599</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>279016.60091411</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>264229.049667442</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>258943.967255994</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>281540.350306148</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>302967.660275207</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>316944.88695509</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>318200.552474306</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>326922.355542666</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>370245.988275054</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>392198.271019119</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>438993.36984693</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>434234.975444001</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>443149.088286452</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>546947.779828069</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>601993.047812866</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>635504.663168633</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>655963.195157108</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>694981.852582076</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>661834.416467527</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>645310.663722735</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8622.5614534511</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>18963.6440621816</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20793.7238027063</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20831.3849758788</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21818.9440765941</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>25146.3991406932</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23575.6214492794</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21421.147200857</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19845.5041697561</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19691.3368700133</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19642.7968615127</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21443.679101754</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21790.1106509783</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22397.8491933754</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20785.1476619886</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21237.4444817836</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20757.2652580364</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22968.843691247</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22918.8128578762</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23460.8018376122</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27745.2459734001</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>25547.8036979477</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>27372.4481215017</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>29085.6405573095</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>33158.7752594279</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>32673.586532076</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>32821.6214532973</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>968.105380029104</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1253.15576402529</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1319.3780808171</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1370.19686016607</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1378.17445273437</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1733.20211767098</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1701.54287170635</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1707.71838708172</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1576.89302285566</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1529.90131848712</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1572.89712152628</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1713.73417909436</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1893.72748440034</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1892.38209909256</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1864.96348859019</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2078.71798516834</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2121.76325875435</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2422.97904985043</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2575.21251803615</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2720.65434517119</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3610.15390273475</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3513.64036048121</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3877.72860813911</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3623.46550657563</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4025.7690255289</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3991.68836870628</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4030.40554720506</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6262.6021774703</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13032.5699783962</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14420.9510830259</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14087.3969486314</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13346.0956986545</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16460.4058319565</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>15267.6419547068</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15693.1487196224</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14901.3696692626</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14678.6618812254</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15671.8550974492</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16277.5313777544</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>17226.511746416</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15804.4749283288</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>15275.1147814526</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14463.0322570659</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13624.8851859583</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15558.4974523401</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15587.8909402175</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>17327.5349215843</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18078.8342558397</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>18716.2024464566</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18398.948193316</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>20710.862862495</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23421.6152769052</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>21363.9654040359</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>22054.441355289</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>311177.577710037</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>308959.412693899</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>366561.313786031</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>410595.560273308</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>422613.050139538</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>532638.938489032</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>524934.730120079</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>493654.685427091</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>463283.626981525</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>437410.466545037</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>481073.840893657</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>514810.869030501</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>548368.36242551</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>551932.325449173</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>578048.272072113</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>675383.656115263</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>719062.942185948</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>803620.527829802</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>802473.994345973</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>863798.032920876</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1227399.50234872</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>985447.604666279</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>869131.338422097</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>1056232.00185016</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>1165856.20821547</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>1192779.46180961</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>1205804.97506051</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1351.88229161115</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1148.36591148106</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1407.23171783502</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1485.4834727571</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1603.21121302698</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1949.43644588192</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2042.35259310154</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1598.17535475791</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1775.62826597062</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1599.04339333678</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1754.36742143967</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1852.28869292292</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1881.2318171982</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1897.56156569654</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1874.91411974969</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2115.07795823609</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2265.92350748879</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2527.24510230805</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2456.83349198589</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2940.4074263533</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3679.10198321583</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3428.78124741186</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3995.45600338556</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4385.54054475918</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5517.95660620015</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5321.27544662351</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5443.45392343964</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>31791.7182951521</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>44989.0007306907</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>52394.2641935213</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>55446.0273306084</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>60506.5676519605</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>72586.7651151462</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>71355.5547774886</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>71764.6310522946</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>61405.6065960999</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>64132.2648154363</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>68182.4028131933</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>76322.1428721186</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>81426.8696496321</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>83325.4703586432</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>80987.1065124287</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>90508.9329727647</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>90850.1401184701</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>98759.023026215</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>96923.0422204836</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>95108.6307940981</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>108478.180821175</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>98891.9493511959</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>102737.329805891</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>101312.204321661</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>111090.518812533</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>108535.490698564</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>107992.729168959</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>102140.272563942</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>187564.683178516</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>204055.766580816</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>205744.007807042</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>212803.892135022</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>244332.159714937</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>245212.139774671</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>227891.731460324</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>200403.661575475</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>189892.261873453</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>204125.714816253</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>221924.192895924</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>236422.890482232</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>244542.911342615</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>246463.009954724</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>277590.511767205</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>279462.006886689</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>307094.619927962</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>299952.450664091</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>306603.210041288</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>349656.558901046</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>321145.898697688</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>331100.487456841</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>363648.212309237</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>389616.899706207</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>398664.780438851</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>407703.267336757</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20926.8976093966</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>44011.4627078967</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>46504.7430175768</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>48068.1694878053</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>56458.4300235234</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>66809.2149248152</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>67047.0219908535</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>66345.1677096935</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>60521.578152019</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>57759.3941856796</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>62181.0000140295</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>65234.321116371</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>68071.4738476531</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>67453.2414634759</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>65116.7978609514</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>73163.7158287618</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>74922.2748356161</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>79396.9590376929</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>73804.2483432693</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>76303.5419380096</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>84950.6780923756</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>79288.682375854</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>84824.0803852954</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>87552.6538184287</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>94573.8072457474</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>92685.811918308</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>91247.8087433641</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>72149.8915877251</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>124635.882491591</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>133387.098989124</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>161090.326914908</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>169572.677839713</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>201482.932719992</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>202469.630413696</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>183358.425537321</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>152293.896737878</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>141894.248005507</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>152197.301403947</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>149176.12708094</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>160852.390710852</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>161127.173200392</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>156626.140504067</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>175038.655063738</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>180340.870729082</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>192846.216210231</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>179001.365839061</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>217051.162998134</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>237837.211212679</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>230300.201977265</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>245052.26842542</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>259360.242088139</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>299565.09433983</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>318423.890289232</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>303200.677114002</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>300964.807258739</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>638222.281758151</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>664354.338894303</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>636072.410391628</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>677739.804921049</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>920468.162478458</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>942422.901495472</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>826506.356652088</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>807591.55280361</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>810708.500296652</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>788681.278375357</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>932720.926097616</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>948760.818240766</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>974675.674195379</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>935148.374891104</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>1072005.78021561</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1.004</t>
+          <t>1150168.35456443</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>1099179.02597127</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.095</t>
+          <t>1261112.44317386</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1320064.38731366</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1268829.96080439</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>944779.593996536</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>967397.83828792</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>1089080.01775149</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1206357.10503309</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>1182078.28939763</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>1182295.87759609</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15581.5027193121</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>26306.2641068208</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>29572.6212790908</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>30234.7199555176</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>31244.1573604842</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35574.4368627119</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34117.5468033844</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>32795.7054425615</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29938.2958834332</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29355.9745140157</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>31296.2482279683</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34381.6118077942</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35933.1483728328</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>37172.8606240562</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36626.7746596108</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>38891.3070510625</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>39761.9986382911</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>44228.8352487957</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>43490.113722287</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>44625.5053036445</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>52426.5781520979</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>50165.1610704164</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>51589.1955444206</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>54414.5826223858</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>58878.9463173784</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>57884.0959810489</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>59652.9467970158</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5032.49500152948</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10939.7580504232</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11684.9330095595</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11685.1138051102</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12194.9534058101</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14241.0275183889</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13950.6004861404</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13831.3514099932</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12868.0539341058</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11790.0569129439</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13131.7205549405</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14492.3322941983</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14879.0795475053</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>15420.6173081119</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14919.3616430659</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16175.5764015647</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16377.0179185771</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>17312.5331948475</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16559.2884760979</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>17057.1591568148</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>18699.8498116056</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>17053.054611902</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18409.0191036477</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18381.8108048778</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>21361.4795935332</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>20531.7968990677</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>21320.4803606758</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16216.1012350291</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34711.6643196869</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>37906.2810044134</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>39639.434186122</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>38353.8764648688</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>51597.206989708</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>52114.9485712985</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>49168.8987349637</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>45592.283945936</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>43691.3372318353</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>46855.1368284224</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>51494.443132875</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>54041.3474142226</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>55111.831236771</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>54318.1227119598</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>59935.4952047569</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>63930.1353530134</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>71424.997620439</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>69603.2328912996</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>71260.8559369609</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>77216.4884239197</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>71148.872996985</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>72526.9567830769</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>71729.8297027107</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>75450.1655020536</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>72256.3319352377</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>68731.1213940481</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>133326.535551664</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>253632.64166146</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>283880.837662982</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>290587.738434137</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>313000.915344429</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>378735.414064643</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>369292.383767033</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>383217.405197155</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>337986.668159811</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>322104.971657848</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>359127.108491775</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>394788.476887471</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>364871.471060206</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>352273.233121067</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>363551.658050102</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>396962.038512664</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>440817.025436357</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>522461.610154175</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>535531.707817454</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>529194.558807264</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>556374.820760488</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>578630.469727778</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>584639.755760195</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>545009.513306493</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>499624.96941265</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>496091.354908447</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>487605.54262187</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>62723.3523375914</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>102135.575491153</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>111712.850525367</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>114928.25951292</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>115487.607871226</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>135865.55043306</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>136156.174011587</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>109924.850729575</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>110735.647434274</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>114233.182327732</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>125303.718043012</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>128633.471577937</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>142319.368272282</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>140356.833545414</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>132575.441775352</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>158911.878238987</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>158006.690032979</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>198112.385378625</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>194523.805316731</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>192177.968625225</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>221745.356466685</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>231000.562947564</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>243594.009115919</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>249420.305786395</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>258234.639331617</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>261501.546994986</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>251644.784774334</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>552443.242424044</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>778780.229740451</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>856228.546681964</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>712448.43063367</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>957867.054622699</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1152048.97145324</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1161769.73736672</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>1118909.02475144</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>1018665.59363232</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>753487.488632467</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>1073275.05964987</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>874860.574711841</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1227514.44134972</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1243665.98413753</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.074</t>
+          <t>1230438.71460856</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1329009.79033094</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>1380350.39976139</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1086725.032022</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1532923.32780831</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1473429.33355329</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1716356.27915546</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>1984355.61564087</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>1.784</t>
+          <t>2119431.30603655</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1.797</t>
+          <t>2136479.58118797</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>2294812.30404401</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>2291991.35919685</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1.912</t>
+          <t>2288040.62168198</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>26.098</t>
+          <t>30008346.0539386</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>26.229</t>
+          <t>30757208.3180457</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29.154</t>
+          <t>34008664.0809212</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30.594</t>
+          <t>35318238.1016596</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>32.707</t>
+          <t>37707194.583684</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>39.713</t>
+          <t>45758027.2756815</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>40.237</t>
+          <t>46312272.2155776</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>39.523</t>
+          <t>45416275.2873675</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>36.779</t>
+          <t>42163862.7084468</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>36.332</t>
+          <t>41523239.2596369</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>39.436</t>
+          <t>45198436.9467397</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>42.799</t>
+          <t>48941284.8196848</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>44.834</t>
+          <t>51469613.0898277</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>45.941</t>
+          <t>52274214.492323</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>45.281</t>
+          <t>51867519.2523628</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>52.418</t>
+          <t>60145823.0731874</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>55.632</t>
+          <t>63759417.9476912</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>61.53</t>
+          <t>70533697.7544693</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>61.131</t>
+          <t>70411069.3724331</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>63.261</t>
+          <t>73421536.4305263</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>71.351</t>
+          <t>83777475.7984412</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>72.891</t>
+          <t>85950787.5027791</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>76.341</t>
+          <t>90719519.9608979</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>78.42</t>
+          <t>93257290.3648926</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>83.845</t>
+          <t>100428968.218163</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>86.82</t>
+          <t>103857617.145691</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>88.679</t>
+          <t>106132211.630627</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6893.17988693454</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16341.8204580601</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>17736.2515730306</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19293.3693141263</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>19781.6118253618</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>22112.8895796762</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23124.4675619291</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21601.8887876932</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20443.6468981525</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20197.2587729895</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22442.0758693705</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23321.0011138066</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23331.0927030154</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>24363.8709708707</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>23334.7035113537</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26056.8138641446</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>25883.4105784514</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27707.0199432417</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>25969.6528002534</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>25381.4288898313</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>28302.623078304</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>25562.817606079</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>28221.6303930077</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>28062.3163014193</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>30652.3434554873</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>29217.8829533982</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>29756.7576607712</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14796.4094211837</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>29437.6272937021</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26672.0418663627</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32593.4773303903</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34226.3880434959</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34674.3051589144</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35543.6957217698</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35984.7752113634</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>31531.0291549341</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>37999.7015742984</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32657.8579755632</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35612.0027765838</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>37639.3485314292</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>47887.7521633835</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>36656.1343977328</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>53779.8773413248</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>43907.9595829005</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>62785.7079511003</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>61394.0521788496</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>59756.3286163351</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>66576.7901601073</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>63896.6968315118</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>67867.6517751313</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>62744.0056066995</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>63621.6680754817</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>62467.866909189</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>63102.6451318574</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8598.1189651664</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18078.4236882611</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>20192.8502779986</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21675.5972384948</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22996.3692529467</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27602.070581496</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26579.6903766499</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26058.2970476506</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>24912.7599638194</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>22524.3714975796</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>24164.7375599942</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>26924.442867472</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28728.3259632796</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29866.8856277388</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29310.3713230429</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34284.552257314</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35736.1343307639</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>40932.6520685389</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>40049.5571750624</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>40977.7273931491</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>44053.1070442086</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>36852.8015134705</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>36976.1082919789</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>36139.3128497096</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>37786.9689475723</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>35516.1119455761</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>36400.9154206358</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>58777.0330418012</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>132580.242969618</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>143784.021724196</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>144973.223580274</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>144460.175150271</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>165312.115253483</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>145366.678206441</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>133964.087744538</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>128304.295345234</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>122413.189974938</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>132049.846322701</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>140301.575133457</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>154382.187627526</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>162767.6158976</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>159754.546551824</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>176053.306247709</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>182103.818032067</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>211948.992371354</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>210626.5315609</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>190945.742220539</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>207547.270090426</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>204304.315490437</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>213766.818060694</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>211941.435417546</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>234621.524151133</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>226103.033825086</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>218466.20360419</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.958</t>
+          <t>4551368.26720597</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.945</t>
+          <t>3453692.75738053</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.409</t>
+          <t>3976577.72548952</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>3.741</t>
+          <t>4318219.06735673</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4.477</t>
+          <t>5160932.80580631</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.442</t>
+          <t>6270577.80107795</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5.513</t>
+          <t>6345255.0107193</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>5.688</t>
+          <t>6535708.32018757</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>5.523</t>
+          <t>6331348.01563615</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>5.806</t>
+          <t>6635836.11287968</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>6.493</t>
+          <t>7441603.86360285</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>6.916</t>
+          <t>7909010.80717277</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>7.241</t>
+          <t>8312666.97167346</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>7.954</t>
+          <t>9050609.53977096</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>7.925</t>
+          <t>9078149.83551416</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>9.549</t>
+          <t>10956515.9974369</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>10.022</t>
+          <t>11486069.180023</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>11.112</t>
+          <t>12738094.0383485</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>10.951</t>
+          <t>12613194.9251526</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>11.124</t>
+          <t>12910463.2185897</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>12.095</t>
+          <t>14201113.6125468</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>11.797</t>
+          <t>13910624.4513409</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>14581078.031184</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12.181</t>
+          <t>14485619.0422367</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>12.742</t>
+          <t>15262473.4786094</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13.034</t>
+          <t>15592313.4252421</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>13.291</t>
+          <t>15906251.6438126</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>645332.560947545</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>1041275.34129811</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>1151772.41156606</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1221197.89740717</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>1264674.61900467</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>1505272.70464493</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1547113.80418115</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>1507817.52738877</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1455012.96339948</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1442994.57322765</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1528001.96858845</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1674035.660853</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1775046.98453271</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1917068.7948715</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>2012634.02400981</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2.107</t>
+          <t>2417332.08911698</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>2.324</t>
+          <t>2663150.12177971</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>2886303.01236256</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2.476</t>
+          <t>2851728.48513298</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2.395</t>
+          <t>2780015.76667249</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>2.571</t>
+          <t>3018492.04983671</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>3099020.88582831</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2.527</t>
+          <t>3002673.16583829</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>2.494</t>
+          <t>2966293.61150806</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>2821936.83146256</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2.201</t>
+          <t>2633418.66460569</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>2502285.32547801</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>1153359.50556486</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1744350.20975149</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>1893391.76858763</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.739</t>
+          <t>2006974.27610458</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>2101510.78978582</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2.125</t>
+          <t>2448931.72858054</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.966</t>
+          <t>2262418.50709583</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>2348924.61003724</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2.006</t>
+          <t>2299803.17949063</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2159989.90191853</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2.003</t>
+          <t>2296088.25545141</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>2573747.57690434</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2.361</t>
+          <t>2710744.67544488</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2.267</t>
+          <t>2579725.18798996</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2.246</t>
+          <t>2573235.06905901</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2.867</t>
+          <t>3289807.01831899</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>2.721</t>
+          <t>3119081.06647521</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>3440516.68173086</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2.939</t>
+          <t>3385609.40142728</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>3.083</t>
+          <t>3578434.09817533</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>2.974</t>
+          <t>3491691.22537431</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2.526</t>
+          <t>2978342.75109835</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2.626</t>
+          <t>3120356.94214853</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>2.852</t>
+          <t>3391602.18160386</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3845468.97025815</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>4076274.22653772</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>3.437</t>
+          <t>4113939.66105375</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.073</t>
+          <t>3533336.21426342</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2.834</t>
+          <t>3323122.14677924</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3697594.42449748</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>3.423</t>
+          <t>3950958.84057472</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3.663</t>
+          <t>4222971.29068318</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.572</t>
+          <t>5267741.29089775</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4.589</t>
+          <t>5281710.88108188</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>4.598</t>
+          <t>5283067.9765816</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>4.385</t>
+          <t>5026771.72286111</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>4.374</t>
+          <t>4998581.27539024</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>4.811</t>
+          <t>5513538.22275203</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>5.285</t>
+          <t>6043301.56217104</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>5.554</t>
+          <t>6375978.42466799</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>5.906</t>
+          <t>6720279.93633029</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>5.994</t>
+          <t>6865803.10587427</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>7.053</t>
+          <t>8092963.84985542</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>7.659</t>
+          <t>8777425.57914397</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>8.582</t>
+          <t>9838174.11691194</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>8.577</t>
+          <t>9879436.38872863</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>9.255</t>
+          <t>10741227.3607367</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>12316448.6471808</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>10.363</t>
+          <t>12220224.8052394</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>10.341</t>
+          <t>12288995.4471975</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10.264</t>
+          <t>12205960.681708</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>10.899</t>
+          <t>13054396.7263584</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11.397</t>
+          <t>13633542.8483302</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>11.442</t>
+          <t>13693865.4089957</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>270224.344206485</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>233675.001020081</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>256235.849058038</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>266666.789317064</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>271723.980036801</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>339911.596204482</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>332519.005281281</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>388878.030827046</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>359980.25601565</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>389537.151183601</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>446231.86680783</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>515483.103710161</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>622956.58668909</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>665509.103283279</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>665348.612195092</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>812554.933118717</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>844554.253928744</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>933594.77305766</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>942011.262049535</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>913053.297442521</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>972988.941649571</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>902644.182590126</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>935057.395439721</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>925682.449362454</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1020665.99557454</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>1061070.01974121</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>1083016.30518616</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
